--- a/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0001T0006Z000C1N5_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0001T0006Z000C1N5_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>20.4658251727117</v>
+        <v>3.325696590565651</v>
       </c>
       <c r="D2" t="n">
-        <v>32.65348373451139</v>
+        <v>5.306191106858101</v>
       </c>
       <c r="E2" t="n">
-        <v>9.595195571820337</v>
+        <v>1.559219280420805</v>
       </c>
       <c r="F2" t="n">
-        <v>6.748445204687827</v>
+        <v>1.096622345761772</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.62853940902552</v>
+        <v>4.489637653966648</v>
       </c>
       <c r="D3" t="n">
-        <v>28.51348450420833</v>
+        <v>4.633441231933854</v>
       </c>
       <c r="E3" t="n">
-        <v>9.595195571820337</v>
+        <v>1.559219280420805</v>
       </c>
       <c r="F3" t="n">
-        <v>6.748445204687827</v>
+        <v>1.096622345761772</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>43.43343115064918</v>
+        <v>7.057932561980492</v>
       </c>
       <c r="D4" t="n">
-        <v>44.4428532191007</v>
+        <v>7.221963648103864</v>
       </c>
       <c r="E4" t="n">
-        <v>9.595195571820337</v>
+        <v>1.559219280420805</v>
       </c>
       <c r="F4" t="n">
-        <v>6.748445204687827</v>
+        <v>1.096622345761772</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
